--- a/tests/features/f7_board_tx.xlsx
+++ b/tests/features/f7_board_tx.xlsx
@@ -437,7 +437,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>a motor on its own transformer under the board, and one with no load yet</t>
+          <t>transformers off an LV board: a motor supply under it, one with no load, an LV/LV one with a sub-board and a motor</t>
         </is>
       </c>
     </row>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -852,6 +852,154 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LV/LV tx</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>100 kVA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0.4/0.23 kV</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>MSB</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SB3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LV Busbar</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>230 V board</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>200 A</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>230 V</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Feeder</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Sockets</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>32 A</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>230 V</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>MCB</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SB3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Pump</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Small motor</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>5 kW</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>230 V</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CB</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
